--- a/Daten/Daten/Materials/MateriallisteLCAMP.xlsx
+++ b/Daten/Daten/Materials/MateriallisteLCAMP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\kdRupp\Source\Repos\LCAMP\Daten\Materials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\kdRupp\Source\Repos\LCAMP-DHBW\Daten\Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2FDD7B-0B6B-4412-80E8-A45B878C0689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922E7D7D-7593-4805-931A-554F0630C2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71748" yWindow="4512" windowWidth="39336" windowHeight="23244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47436" yWindow="2760" windowWidth="41268" windowHeight="18768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="184">
   <si>
     <t>Name</t>
   </si>
@@ -544,6 +544,39 @@
   </si>
   <si>
     <t>Fx</t>
+  </si>
+  <si>
+    <t>PLA Filament  HellGrün</t>
+  </si>
+  <si>
+    <t>HellGrün</t>
+  </si>
+  <si>
+    <t>HellGrünLight</t>
+  </si>
+  <si>
+    <t>FF88E788</t>
+  </si>
+  <si>
+    <t>FF7CA37C</t>
+  </si>
+  <si>
+    <t>FFFC8EAC</t>
+  </si>
+  <si>
+    <t>FlamigoPink</t>
+  </si>
+  <si>
+    <t>PLA Filament  Pink</t>
+  </si>
+  <si>
+    <t>PLA Filament Yellow</t>
+  </si>
+  <si>
+    <t>FFFFEF00</t>
+  </si>
+  <si>
+    <t>Gelb</t>
   </si>
 </sst>
 </file>
@@ -601,9 +634,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -884,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.44140625" customWidth="1"/>
@@ -977,7 +1011,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -985,19 +1019,19 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
+      <c r="D5" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -1005,19 +1039,19 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
-        <v>21</v>
+      <c r="D6" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -1026,18 +1060,18 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="F7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -1046,566 +1080,646 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>183</v>
+      </c>
+      <c r="F11" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" t="s">
-        <v>146</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="F22" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="F31" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F33" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" t="s">
+        <v>120</v>
+      </c>
+      <c r="E36" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" t="s">
+        <v>125</v>
+      </c>
+      <c r="E37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>133</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" t="s">
         <v>134</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C40" t="s">
         <v>48</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D40" t="s">
         <v>135</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E40" t="s">
         <v>68</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F40" t="s">
         <v>168</v>
       </c>
     </row>
